--- a/Actividad_2/Analisis_Suma_Lista.xlsx
+++ b/Actividad_2/Analisis_Suma_Lista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajos_Universidad\5to_Semestre\Programación III\Talleres\Programacion_III\Actividad_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B825CC8A-E9DB-459B-AD70-3593C3939D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB93DDE-3318-427D-99DD-3A5DEF542470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0D9BCB48-0F87-4F02-A586-2AA8F0A8778E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="87">
   <si>
     <t>Divide y venceras para la suma de numeros de una lista</t>
   </si>
@@ -155,272 +155,721 @@
     <t>11+67</t>
   </si>
   <si>
-    <t>suma_lista
-([17,19])
-espera [17]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([17,19])
-izq=17, espera [19]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2])
-mitad=1</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2])
-espera [1]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2])
-izq=1, espera [2]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([3,5])
-mitad=1</t>
-  </si>
-  <si>
-    <t>suma_lista
-([3,5])
-espera [3]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([3,5])
-izq=3, espera [5]</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7,11])
-mitad=1</t>
-  </si>
-  <si>
-    <t>suma_lista
-([13,17,19])
-mitad=1</t>
-  </si>
-  <si>
-    <t>suma_lista
-([13,17,19])
-izq=13, espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-mitad=2</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-espera izq</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-izq=3, espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-der=8, combina</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7,11,13,17,19])
-mitad=2</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7..19])
-espera izq</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7..19])
-izq=18, espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7..19])
-espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-mitad=4</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-espera izq</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-izq=11, espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-espera der</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-der=67, combina</t>
+    <t>suma_lista([1])
+1</t>
+  </si>
+  <si>
+    <t>suma_lista([2])
+2</t>
+  </si>
+  <si>
+    <t>suma_lista([3])
+3</t>
+  </si>
+  <si>
+    <t>suma_lista([5])
+5</t>
+  </si>
+  <si>
+    <t>suma_lista([7])
+7</t>
+  </si>
+  <si>
+    <t>suma_lista([11])
+11</t>
+  </si>
+  <si>
+    <t>suma_lista([13])
+13</t>
+  </si>
+  <si>
+    <t>suma_lista([17])
+17</t>
+  </si>
+  <si>
+    <t>suma_lista([19])
+19</t>
+  </si>
+  <si>
+    <t>Ejecución de la Pila</t>
+  </si>
+  <si>
+    <t>inicio 0</t>
+  </si>
+  <si>
+    <t>fin 8</t>
+  </si>
+  <si>
+    <t>0   0</t>
+  </si>
+  <si>
+    <t>1   1</t>
+  </si>
+  <si>
+    <t>2   2</t>
+  </si>
+  <si>
+    <t>3   3</t>
+  </si>
+  <si>
+    <t>4    4</t>
+  </si>
+  <si>
+    <t>5   5</t>
+  </si>
+  <si>
+    <t>6    6</t>
+  </si>
+  <si>
+    <t>7    7</t>
+  </si>
+  <si>
+    <t>8    8</t>
   </si>
   <si>
     <t>main
 lista=[1..19]
-sumar_lista</t>
-  </si>
-  <si>
-    <t>suma_lista([1])
-1</t>
-  </si>
-  <si>
-    <t>suma_lista([2])
-2</t>
-  </si>
-  <si>
-    <t>suma_lista([3])
-3</t>
-  </si>
-  <si>
-    <t>suma_lista([5])
-5</t>
-  </si>
-  <si>
-    <t>suma_lista([7])
-7</t>
-  </si>
-  <si>
-    <t>suma_lista([11])
-11</t>
-  </si>
-  <si>
-    <t>suma_lista([13])
-13</t>
-  </si>
-  <si>
-    <t>suma_lista([17])
-17</t>
-  </si>
-  <si>
-    <t>suma_lista([19])
-19</t>
+sumar_lista (lista)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1..19])
+izq = [1,2,3,5]
+der = [7,11,13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sumar(izq )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2,3,5])
+izq = [1,2]
+der = [3,5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sumar(izq )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <t>Divide y vencerás para la suma de números de una lista</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2])
+izq = [1]
+der = [2]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sumar(izq )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2])
+izq = [1]
+der = [2]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2])
+izq = [1]
+der = [2]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + 2 = 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2,3,5])
+izq = [1,2]
+der = [3,5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([3,5])
+izq = [3]
+der = [5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">sumar(izq ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([3,5])
+izq = [3]
+der = [5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([3,5])
+izq = [3]
+der = [5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ 5 = 8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1,2,3,5])
+izq = [1,2]
+der = [3,5]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + 8 = 11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1..19])
+izq = [1,2,3,5]
+der = [7,11,13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11])
+izq = [7]
+der = [11]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">sumar(izq ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11])
+izq = [7]
+der = [11]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11])
+izq = [7]
+der = [11]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ 11 = 18</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11,13,17,19])
+izq = [7,11]
+der = [13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">sumar(izq ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11,13,17,19])
+izq = [7,11]
+der = [13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([13,17,19])
+izq = [13]
+der = [17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sumar(izq )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([13,17,19])
+izq = [13]
+der = [17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([17,19])
+izq = [17]
+der = [19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sumar(izq )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([17,19])
+izq = [17]
+der = [19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + sumar(der)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([17,19])
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+19 = 36</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([13,17,19])
+izq = [13]
+der = [17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + 36 = 49</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([7,11,13,17,19])
+izq = [7,11]
+der = [13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+ 49 = 67</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">suma_lista
+([1..19])
+izq = [1,2,3,5]
+der = [7,11,13,17,19]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + 67 </t>
+    </r>
   </si>
   <si>
     <t>main
+lista=[1..19]
 resultado = 78</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1..19])
-11+67 = 78</t>
-  </si>
-  <si>
-    <t>suma_lista
-([13,17,19])
-13</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7,11])
-izq=7, 11</t>
-  </si>
-  <si>
-    <t>Ejecución de la Pila</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7,11])
-11</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7..19])
-18+49 = 67</t>
-  </si>
-  <si>
-    <t>suma_lista
-([13,17,19])
-13+36 = 49</t>
-  </si>
-  <si>
-    <t>suma_lista
-([17,19])
-17+19 = 36</t>
-  </si>
-  <si>
-    <t>suma_lista
-([7,11])
-7+11 = 18</t>
-  </si>
-  <si>
-    <t>suma_lista
-([3,5])
-3+5 = 8</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2])
-1+2 = 3</t>
-  </si>
-  <si>
-    <t>suma_lista
-([1,2,3,5])
-3+8 = 11</t>
-  </si>
-  <si>
-    <t>inicio 0</t>
-  </si>
-  <si>
-    <t>fin 8</t>
-  </si>
-  <si>
-    <t>0   0</t>
-  </si>
-  <si>
-    <t>1   1</t>
-  </si>
-  <si>
-    <t>2   2</t>
-  </si>
-  <si>
-    <t>3   3</t>
-  </si>
-  <si>
-    <t>4    4</t>
-  </si>
-  <si>
-    <t>5   5</t>
-  </si>
-  <si>
-    <t>6    6</t>
-  </si>
-  <si>
-    <t>7    7</t>
-  </si>
-  <si>
-    <t>8    8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,15 +915,33 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Arial Black"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="28"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Arial Black"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -494,12 +961,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -572,6 +1033,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,7 +1369,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -911,9 +1378,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -923,52 +1389,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
@@ -980,16 +1428,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
@@ -998,100 +1446,120 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="23" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="24" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="18" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="22" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="19" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="8">
     <cellStyle name="20% - Énfasis1" xfId="1" builtinId="30"/>
-    <cellStyle name="40% - Énfasis2" xfId="3" builtinId="35"/>
-    <cellStyle name="40% - Énfasis5" xfId="6" builtinId="47"/>
-    <cellStyle name="40% - Énfasis6" xfId="7" builtinId="51"/>
+    <cellStyle name="40% - Énfasis5" xfId="5" builtinId="47"/>
+    <cellStyle name="40% - Énfasis6" xfId="6" builtinId="51"/>
     <cellStyle name="60% - Énfasis1" xfId="2" builtinId="32"/>
-    <cellStyle name="60% - Énfasis2" xfId="4" builtinId="36"/>
-    <cellStyle name="60% - Énfasis3" xfId="5" builtinId="40"/>
-    <cellStyle name="60% - Énfasis6" xfId="8" builtinId="52"/>
+    <cellStyle name="60% - Énfasis2" xfId="3" builtinId="36"/>
+    <cellStyle name="60% - Énfasis3" xfId="4" builtinId="40"/>
+    <cellStyle name="60% - Énfasis6" xfId="7" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1118,9 +1586,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1220698</xdr:colOff>
+      <xdr:colOff>204698</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>721178</xdr:rowOff>
+      <xdr:rowOff>435428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1468,12 +1936,12 @@
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:12" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="51"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="43"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1482,12 +1950,12 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1496,10 +1964,10 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1508,16 +1976,16 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="16" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="2"/>
@@ -1528,7 +1996,7 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -1537,7 +2005,7 @@
       <c r="E9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="2"/>
@@ -1548,7 +2016,7 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="3">
@@ -1557,7 +2025,7 @@
       <c r="E10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="2"/>
@@ -1568,7 +2036,7 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3">
@@ -1577,7 +2045,7 @@
       <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="2"/>
@@ -1588,7 +2056,7 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="4">
@@ -1597,7 +2065,7 @@
       <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="19">
         <v>1</v>
       </c>
       <c r="G12" s="2"/>
@@ -1608,7 +2076,7 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="4">
@@ -1617,7 +2085,7 @@
       <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="19">
         <v>2</v>
       </c>
       <c r="G13" s="2"/>
@@ -1628,7 +2096,7 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -1637,7 +2105,7 @@
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="20">
         <v>3</v>
       </c>
       <c r="G14" s="2"/>
@@ -1648,7 +2116,7 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="3">
@@ -1657,7 +2125,7 @@
       <c r="E15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="2"/>
@@ -1668,7 +2136,7 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="4">
@@ -1677,7 +2145,7 @@
       <c r="E16" s="4">
         <v>3</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="18">
         <v>3</v>
       </c>
       <c r="G16" s="2"/>
@@ -1688,7 +2156,7 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="4">
@@ -1697,7 +2165,7 @@
       <c r="E17" s="4">
         <v>5</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="19">
         <v>5</v>
       </c>
       <c r="G17" s="2"/>
@@ -1708,7 +2176,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -1717,7 +2185,7 @@
       <c r="E18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="20">
         <v>8</v>
       </c>
       <c r="G18" s="2"/>
@@ -1728,16 +2196,16 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="45">
         <v>11</v>
       </c>
       <c r="G19" s="2"/>
@@ -1748,16 +2216,16 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="3:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="30">
         <v>2</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="32" t="s">
         <v>30</v>
       </c>
       <c r="G20" s="2"/>
@@ -1768,7 +2236,7 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="21" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="5">
@@ -1777,13 +2245,13 @@
       <c r="E21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="22" t="s">
         <v>30</v>
       </c>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="6">
@@ -1792,13 +2260,13 @@
       <c r="E22" s="6">
         <v>7</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="23">
         <v>7</v>
       </c>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="6">
@@ -1807,13 +2275,13 @@
       <c r="E23" s="6">
         <v>11</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="23">
         <v>11</v>
       </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="21" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="6" t="s">
@@ -1822,13 +2290,13 @@
       <c r="E24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="20">
         <v>18</v>
       </c>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="5">
@@ -1837,13 +2305,13 @@
       <c r="E25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="20">
         <v>13</v>
       </c>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="5">
@@ -1852,13 +2320,13 @@
       <c r="E26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="22" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="6">
@@ -1867,13 +2335,13 @@
       <c r="E27" s="6">
         <v>17</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="23">
         <v>17</v>
       </c>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="6">
@@ -1882,13 +2350,13 @@
       <c r="E28" s="6">
         <v>19</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="23">
         <v>19</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -1897,14 +2365,14 @@
       <c r="E29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="20">
         <v>36</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -1913,35 +2381,35 @@
       <c r="E30" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="20">
         <v>49</v>
       </c>
     </row>
     <row r="31" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="41" t="s">
+      <c r="D31" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="46">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="34" t="s">
+      <c r="E32" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="28">
         <v>78</v>
       </c>
     </row>
@@ -1957,448 +2425,823 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8C9862-3CC0-4A32-8430-1C2C90B29159}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" customWidth="1"/>
-    <col min="17" max="17" width="17.7109375" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" customWidth="1"/>
-    <col min="19" max="19" width="16.28515625" customWidth="1"/>
-    <col min="20" max="20" width="18.140625" customWidth="1"/>
-    <col min="21" max="21" width="20.140625" customWidth="1"/>
-    <col min="22" max="22" width="20.42578125" customWidth="1"/>
-    <col min="23" max="23" width="17.5703125" customWidth="1"/>
-    <col min="24" max="24" width="22.85546875" customWidth="1"/>
-    <col min="25" max="25" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" customWidth="1"/>
+    <col min="11" max="11" width="28.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="27.85546875" customWidth="1"/>
+    <col min="16" max="16" width="27.42578125" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="28.140625" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="20" max="20" width="28.85546875" customWidth="1"/>
+    <col min="21" max="21" width="28.85546875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="27.28515625" customWidth="1"/>
+    <col min="23" max="23" width="28.28515625" customWidth="1"/>
+    <col min="24" max="24" width="28.28515625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="27.42578125" customWidth="1"/>
+    <col min="26" max="26" width="27.7109375" style="2" customWidth="1"/>
+    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="28" max="28" width="26.5703125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="27.28515625" customWidth="1"/>
+    <col min="30" max="30" width="22.7109375" style="2" customWidth="1"/>
+    <col min="31" max="31" width="23.140625" customWidth="1"/>
+    <col min="32" max="32" width="20" customWidth="1"/>
+    <col min="33" max="33" width="22.28515625" customWidth="1"/>
+    <col min="34" max="34" width="23.140625" customWidth="1"/>
+    <col min="35" max="35" width="23.28515625" customWidth="1"/>
+    <col min="36" max="36" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-    </row>
-    <row r="3" spans="1:25" ht="42" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:25" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="55"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="K4" s="52" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+    </row>
+    <row r="2" spans="1:36" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+    </row>
+    <row r="3" spans="1:36" ht="42" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+    </row>
+    <row r="4" spans="1:36" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
       <c r="L4" s="53"/>
       <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="14"/>
-    </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="1:25" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-    </row>
-    <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="N4" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="53"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+    </row>
+    <row r="5" spans="1:36" s="2" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+    </row>
+    <row r="6" spans="1:36" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="47"/>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+    </row>
+    <row r="7" spans="1:36" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
       <c r="F7" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="I7" s="7"/>
-      <c r="J7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="O7" s="7"/>
-      <c r="P7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" s="7"/>
+      <c r="V7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC7" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD7" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE7" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF7" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+    </row>
+    <row r="8" spans="1:36" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="53"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="47"/>
+      <c r="K8" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="U8" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="X8" s="47"/>
+      <c r="Y8" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z8" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG8" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+    </row>
+    <row r="9" spans="1:36" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="U7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:25" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="Q9" s="47"/>
+      <c r="R9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="T9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="U9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="V9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="W9" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH9" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+    </row>
+    <row r="10" spans="1:36" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="53"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="P10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="R10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="W10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="X10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH10" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI10" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="S8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="T8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="U8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-    </row>
-    <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="12" t="s">
+      <c r="AJ10" s="1"/>
+    </row>
+    <row r="11" spans="1:36" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="53"/>
+      <c r="B11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="R11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="S11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="T11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="U11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="V11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="W11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="X11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI11" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ11" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-    </row>
-    <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
-      <c r="C10" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="S10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="T10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="V10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y10" s="7"/>
-    </row>
-    <row r="11" spans="1:25" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="S11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="T11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="U11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="V11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="W11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="X11" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y11" s="13" t="s">
-        <v>74</v>
-      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="N4:T4"/>
     <mergeCell ref="A1:C7"/>
-    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="N3:T3"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2438,11 +3281,11 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="15">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="15">
+      <c r="D3" s="9">
         <v>2</v>
       </c>
       <c r="E3" s="1"/>
@@ -2462,12 +3305,12 @@
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>89</v>
+      <c r="B4" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="16" t="s">
-        <v>90</v>
+      <c r="D4" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -2507,10 +3350,10 @@
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="59">
+      <c r="C6" s="44">
         <v>3</v>
       </c>
-      <c r="D6" s="59"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
         <v>3</v>
@@ -2543,78 +3386,78 @@
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="15">
+      <c r="C7" s="9">
         <v>1</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="9">
         <v>2</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="15">
+      <c r="F7" s="9">
         <v>3</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="15">
+      <c r="H7" s="9">
         <v>5</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="15">
+      <c r="J7" s="9">
         <v>7</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="17">
+      <c r="M7" s="11">
         <v>11</v>
       </c>
       <c r="N7" s="1"/>
-      <c r="O7" s="17">
+      <c r="O7" s="11">
         <v>13</v>
       </c>
       <c r="P7" s="1"/>
-      <c r="Q7" s="17">
+      <c r="Q7" s="11">
         <v>17</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="17">
+      <c r="S7" s="11">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="16">
+      <c r="C8" s="10">
         <v>0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="12">
         <v>1</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="16" t="s">
-        <v>91</v>
+      <c r="F8" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="R8" s="19"/>
-      <c r="S8" s="16" t="s">
-        <v>97</v>
+      <c r="H8" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" s="13"/>
+      <c r="S8" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
@@ -2640,65 +3483,65 @@
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="59">
+      <c r="D10" s="44">
         <v>6</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="59">
+      <c r="H10" s="44">
         <v>12</v>
       </c>
-      <c r="I10" s="59"/>
+      <c r="I10" s="44"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="59">
+      <c r="N10" s="44">
         <v>24</v>
       </c>
-      <c r="O10" s="59"/>
+      <c r="O10" s="44"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="59">
+      <c r="Q10" s="44">
         <v>36</v>
       </c>
-      <c r="R10" s="59"/>
+      <c r="R10" s="44"/>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="15">
+      <c r="D11" s="9">
         <v>1</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="9">
         <v>2</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="9">
         <v>3</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="15">
+      <c r="H11" s="9">
         <v>5</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="9">
         <v>7</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="17">
+      <c r="N11" s="11">
         <v>11</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="11">
         <v>13</v>
       </c>
       <c r="P11" s="1"/>
-      <c r="Q11" s="17">
+      <c r="Q11" s="11">
         <v>17</v>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="11">
         <v>19</v>
       </c>
       <c r="S11" s="1"/>
@@ -2706,37 +3549,37 @@
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="16">
+      <c r="D12" s="10">
         <v>0</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="12">
         <v>1</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="12">
         <v>2</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="18">
+      <c r="H12" s="12">
         <v>3</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="12">
         <v>4</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="18">
+      <c r="N12" s="12">
         <v>5</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="12">
         <v>6</v>
       </c>
       <c r="P12" s="1"/>
-      <c r="Q12" s="18">
+      <c r="Q12" s="12">
         <v>7</v>
       </c>
-      <c r="R12" s="16">
+      <c r="R12" s="10">
         <v>8</v>
       </c>
       <c r="S12" s="1"/>
@@ -2766,21 +3609,21 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="59">
+      <c r="F14" s="44">
         <v>18</v>
       </c>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="59">
+      <c r="M14" s="44">
         <v>60</v>
       </c>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -2790,33 +3633,33 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="15">
+      <c r="F15" s="9">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="9">
         <v>2</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="9">
         <v>3</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="9">
         <v>5</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="9">
         <v>7</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="17">
+      <c r="M15" s="11">
         <v>11</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="11">
         <v>13</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="11">
         <v>17</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="11">
         <v>19</v>
       </c>
       <c r="Q15" s="1"/>
@@ -2828,33 +3671,33 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="16">
+      <c r="F16" s="10">
         <v>0</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="12">
         <v>1</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="12">
         <v>2</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="12">
         <v>3</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="12">
         <v>4</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="18">
+      <c r="M16" s="12">
         <v>5</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="12">
         <v>6</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="12">
         <v>7</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="10">
         <v>8</v>
       </c>
       <c r="Q16" s="1"/>
@@ -2907,17 +3750,17 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="59">
+      <c r="G19" s="44">
         <v>78</v>
       </c>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2929,31 +3772,31 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="15">
+      <c r="G20" s="9">
         <v>1</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="9">
         <v>2</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="9">
         <v>3</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="9">
         <v>5</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="9">
         <v>7</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="11">
         <v>11</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="11">
         <v>13</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="11">
         <v>17</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="11">
         <v>19</v>
       </c>
       <c r="P20" s="1"/>
@@ -2967,32 +3810,32 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="18">
+      <c r="G21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="12">
         <v>1</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="12">
         <v>2</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="12">
         <v>3</v>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="12">
         <v>4</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="12">
         <v>5</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="12">
         <v>6</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="12">
         <v>7</v>
       </c>
-      <c r="O21" s="16" t="s">
-        <v>88</v>
+      <c r="O21" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
